--- a/RawTables/Localization.xlsx
+++ b/RawTables/Localization.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="343">
   <si>
     <t>Id</t>
   </si>
@@ -49,231 +49,290 @@
     <t>英文</t>
   </si>
   <si>
+    <t>StartGame</t>
+  </si>
+  <si>
+    <t>开始游戏</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>Achievement</t>
+  </si>
+  <si>
+    <t>成就</t>
+  </si>
+  <si>
+    <t>Achievements</t>
+  </si>
+  <si>
+    <t>Quit</t>
+  </si>
+  <si>
+    <t>退出游戏</t>
+  </si>
+  <si>
+    <t>Sure</t>
+  </si>
+  <si>
+    <t>确定</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>取消</t>
+  </si>
+  <si>
+    <t>Archive</t>
+  </si>
+  <si>
+    <t>选择存档</t>
+  </si>
+  <si>
+    <t>Select Profile</t>
+  </si>
+  <si>
     <t>NewGame</t>
   </si>
   <si>
-    <t>开始游戏</t>
+    <t>新游戏</t>
+  </si>
+  <si>
+    <t>New Game</t>
+  </si>
+  <si>
+    <t>tipsDeleteArc1</t>
+  </si>
+  <si>
+    <t>是否确认删除该存档</t>
+  </si>
+  <si>
+    <t>Are you sure you want to delete this save?</t>
+  </si>
+  <si>
+    <t>tipsDeleteArc2</t>
+  </si>
+  <si>
+    <t>（存档删除后不可恢复）</t>
+  </si>
+  <si>
+    <t>(Cannot be recovered after deletion)</t>
+  </si>
+  <si>
+    <t>tipsCopyArc1</t>
+  </si>
+  <si>
+    <t>是否确认复制该存档</t>
+  </si>
+  <si>
+    <t>Are you sure you want to copy this save file?</t>
+  </si>
+  <si>
+    <t>tipsCopyArc2</t>
+  </si>
+  <si>
+    <t>（存档自动复制到当前第一个新游戏）</t>
+  </si>
+  <si>
+    <t>(The save is automatically copied to the first new game)</t>
+  </si>
+  <si>
+    <t>refuseCopyTips</t>
+  </si>
+  <si>
+    <t>当前存档位置已满
+请删除存档后再复制</t>
+  </si>
+  <si>
+    <t>The current save slot is full. 
+Please delete a save before copying.</t>
+  </si>
+  <si>
+    <t>tipsQuit</t>
+  </si>
+  <si>
+    <t>是否退出游戏</t>
+  </si>
+  <si>
+    <t>Do you want to exit the game?</t>
+  </si>
+  <si>
+    <t>KeySetting</t>
+  </si>
+  <si>
+    <t>键位设置</t>
+  </si>
+  <si>
+    <t>Keyboard Settings</t>
+  </si>
+  <si>
+    <t>SoundSetting</t>
+  </si>
+  <si>
+    <t>音量设置</t>
+  </si>
+  <si>
+    <t>Volume Settings</t>
+  </si>
+  <si>
+    <t>LanguageSetting</t>
+  </si>
+  <si>
+    <t>语言设置</t>
+  </si>
+  <si>
+    <t>Language Settings</t>
+  </si>
+  <si>
+    <t>Music</t>
+  </si>
+  <si>
+    <t>音乐调节</t>
+  </si>
+  <si>
+    <t>Background music</t>
+  </si>
+  <si>
+    <t>SoundEffects</t>
+  </si>
+  <si>
+    <t>音效调节</t>
+  </si>
+  <si>
+    <t>Sound effects</t>
+  </si>
+  <si>
+    <t>Languagetips</t>
+  </si>
+  <si>
+    <t>（主菜单中切换语言）</t>
+  </si>
+  <si>
+    <t>(Switch language in the main menu)</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>选择语言</t>
+  </si>
+  <si>
+    <t>Select Language</t>
+  </si>
+  <si>
+    <t>key1</t>
+  </si>
+  <si>
+    <t>奔跑</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>key2</t>
+  </si>
+  <si>
+    <t>跳跃</t>
+  </si>
+  <si>
+    <t>Jump</t>
+  </si>
+  <si>
+    <t>key3</t>
+  </si>
+  <si>
+    <t>冲刺</t>
+  </si>
+  <si>
+    <t>Dash</t>
+  </si>
+  <si>
+    <t>key4</t>
+  </si>
+  <si>
+    <t>交互</t>
+  </si>
+  <si>
+    <t>Interaction</t>
+  </si>
+  <si>
+    <t>key5</t>
+  </si>
+  <si>
+    <t>抓</t>
+  </si>
+  <si>
+    <t>Grab</t>
+  </si>
+  <si>
+    <t>key6</t>
+  </si>
+  <si>
+    <t>地图</t>
+  </si>
+  <si>
+    <t>Map</t>
+  </si>
+  <si>
+    <t>key7</t>
+  </si>
+  <si>
+    <t>物品栏</t>
+  </si>
+  <si>
+    <t>Backpack</t>
+  </si>
+  <si>
+    <t>key8</t>
+  </si>
+  <si>
+    <t>卡牌库</t>
+  </si>
+  <si>
+    <t>Card Library</t>
+  </si>
+  <si>
+    <t>key9</t>
+  </si>
+  <si>
+    <t>图鉴</t>
+  </si>
+  <si>
+    <t>Collection</t>
+  </si>
+  <si>
+    <t>key10</t>
+  </si>
+  <si>
+    <t>锻造</t>
+  </si>
+  <si>
+    <t>Forging</t>
+  </si>
+  <si>
+    <t>key11</t>
+  </si>
+  <si>
+    <t>重置</t>
+  </si>
+  <si>
+    <t>Reset</t>
+  </si>
+  <si>
+    <t>ESC1</t>
+  </si>
+  <si>
+    <t>继续游戏</t>
   </si>
   <si>
     <t>Continue</t>
   </si>
   <si>
-    <t>继续游戏</t>
-  </si>
-  <si>
-    <t>Setting</t>
-  </si>
-  <si>
-    <t>设置</t>
-  </si>
-  <si>
-    <t>Quit</t>
-  </si>
-  <si>
-    <t>退出游戏</t>
-  </si>
-  <si>
-    <t>Sure</t>
-  </si>
-  <si>
-    <t>确定</t>
-  </si>
-  <si>
-    <t>Cancel</t>
-  </si>
-  <si>
-    <t>取消</t>
-  </si>
-  <si>
-    <t>Archive</t>
-  </si>
-  <si>
-    <t>存档</t>
-  </si>
-  <si>
-    <t>tipsStartAgain1</t>
-  </si>
-  <si>
-    <t>是否确认重新开始游戏</t>
-  </si>
-  <si>
-    <t>Are you sure you want to restart the game?</t>
-  </si>
-  <si>
-    <t>tipsStartAgain2</t>
-  </si>
-  <si>
-    <t>（重新开始后所有存档将被删除）</t>
-  </si>
-  <si>
-    <t>(All saved data will be deleted after restarting)</t>
-  </si>
-  <si>
-    <t>tipsQuit</t>
-  </si>
-  <si>
-    <t>是否退出游戏</t>
-  </si>
-  <si>
-    <t>Do you want to exit the game?</t>
-  </si>
-  <si>
-    <t>KeySetting</t>
-  </si>
-  <si>
-    <t>键位设置</t>
-  </si>
-  <si>
-    <t>Keyboard Settings</t>
-  </si>
-  <si>
-    <t>SoundSetting</t>
-  </si>
-  <si>
-    <t>音量设置</t>
-  </si>
-  <si>
-    <t>Volume Settings</t>
-  </si>
-  <si>
-    <t>LanguageSetting</t>
-  </si>
-  <si>
-    <t>语言设置</t>
-  </si>
-  <si>
-    <t>Language Settings</t>
-  </si>
-  <si>
-    <t>Music</t>
-  </si>
-  <si>
-    <t>音乐调节</t>
-  </si>
-  <si>
-    <t>Background music</t>
-  </si>
-  <si>
-    <t>SoundEffects</t>
-  </si>
-  <si>
-    <t>音效调节</t>
-  </si>
-  <si>
-    <t>Sound effects</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>选择语言</t>
-  </si>
-  <si>
-    <t>Select Language</t>
-  </si>
-  <si>
-    <t>key1</t>
-  </si>
-  <si>
-    <t>奔跑</t>
-  </si>
-  <si>
-    <t>Run</t>
-  </si>
-  <si>
-    <t>key2</t>
-  </si>
-  <si>
-    <t>跳跃</t>
-  </si>
-  <si>
-    <t>Jump</t>
-  </si>
-  <si>
-    <t>key3</t>
-  </si>
-  <si>
-    <t>冲刺</t>
-  </si>
-  <si>
-    <t>Dash</t>
-  </si>
-  <si>
-    <t>key4</t>
-  </si>
-  <si>
-    <t>交互</t>
-  </si>
-  <si>
-    <t>Interaction</t>
-  </si>
-  <si>
-    <t>key5</t>
-  </si>
-  <si>
-    <t>抓</t>
-  </si>
-  <si>
-    <t>Grab</t>
-  </si>
-  <si>
-    <t>key6</t>
-  </si>
-  <si>
-    <t>地图</t>
-  </si>
-  <si>
-    <t>Map</t>
-  </si>
-  <si>
-    <t>key7</t>
-  </si>
-  <si>
-    <t>物品栏</t>
-  </si>
-  <si>
-    <t>Backpack</t>
-  </si>
-  <si>
-    <t>key8</t>
-  </si>
-  <si>
-    <t>卡牌库</t>
-  </si>
-  <si>
-    <t>Card Library</t>
-  </si>
-  <si>
-    <t>key9</t>
-  </si>
-  <si>
-    <t>图鉴</t>
-  </si>
-  <si>
-    <t>Collection</t>
-  </si>
-  <si>
-    <t>key10</t>
-  </si>
-  <si>
-    <t>锻造</t>
-  </si>
-  <si>
-    <t>Forging</t>
-  </si>
-  <si>
-    <t>key11</t>
-  </si>
-  <si>
-    <t>重置</t>
-  </si>
-  <si>
-    <t>Reset</t>
-  </si>
-  <si>
-    <t>ESC1</t>
-  </si>
-  <si>
     <t>ESC2</t>
   </si>
   <si>
@@ -286,13 +345,721 @@
     <t>Return to Home</t>
   </si>
   <si>
-    <t>ESCreMainTips</t>
+    <t>ESCreMainTips1</t>
   </si>
   <si>
     <t>是否确认返回主界面</t>
   </si>
   <si>
     <t>Are you sure you want to return to the main screen?</t>
+  </si>
+  <si>
+    <t>ESCreMainTips2</t>
+  </si>
+  <si>
+    <t>（自动保存游戏进度）</t>
+  </si>
+  <si>
+    <t>(Game progress automatically saved)</t>
+  </si>
+  <si>
+    <t>book1</t>
+  </si>
+  <si>
+    <t>卡牌图鉴</t>
+  </si>
+  <si>
+    <t>Cards</t>
+  </si>
+  <si>
+    <t>book2</t>
+  </si>
+  <si>
+    <t>生物图鉴</t>
+  </si>
+  <si>
+    <t>Biology</t>
+  </si>
+  <si>
+    <t>noCardName</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>noCardDetails</t>
+  </si>
+  <si>
+    <t>暂未获取</t>
+  </si>
+  <si>
+    <t>Not yet obtained</t>
+  </si>
+  <si>
+    <t>card1N</t>
+  </si>
+  <si>
+    <t>攻击卡</t>
+  </si>
+  <si>
+    <t>Attack Card</t>
+  </si>
+  <si>
+    <t>card1D</t>
+  </si>
+  <si>
+    <t>最常见的普通攻击，对指定目标造成x点伤害</t>
+  </si>
+  <si>
+    <t>The most common basic attack, deals X damage to a specified target.</t>
+  </si>
+  <si>
+    <t>card2N</t>
+  </si>
+  <si>
+    <t>防御卡</t>
+  </si>
+  <si>
+    <t>Defense Card</t>
+  </si>
+  <si>
+    <t>card2D</t>
+  </si>
+  <si>
+    <t>最常见的防御，玩家获得x点盾</t>
+  </si>
+  <si>
+    <t>The most common defense, player gains X shield points.</t>
+  </si>
+  <si>
+    <t>card3N</t>
+  </si>
+  <si>
+    <t>得到卡</t>
+  </si>
+  <si>
+    <t>Gain Card</t>
+  </si>
+  <si>
+    <t>card3D</t>
+  </si>
+  <si>
+    <t>指定目标获得x点xx（效果）</t>
+  </si>
+  <si>
+    <t>A specified target gains X points of XX (effect).</t>
+  </si>
+  <si>
+    <t>card4N</t>
+  </si>
+  <si>
+    <t>失去卡</t>
+  </si>
+  <si>
+    <t>Loss Card</t>
+  </si>
+  <si>
+    <t>card4D</t>
+  </si>
+  <si>
+    <t>指定对象失去x点xx</t>
+  </si>
+  <si>
+    <t>A specified target loses X points of XX.</t>
+  </si>
+  <si>
+    <t>card5N</t>
+  </si>
+  <si>
+    <t>重复卡</t>
+  </si>
+  <si>
+    <t>Repeat Card</t>
+  </si>
+  <si>
+    <t>card5D</t>
+  </si>
+  <si>
+    <t>可以直接使用，记录上一张使用的卡牌的属性，打出完全相同的效果</t>
+  </si>
+  <si>
+    <t>Can be used directly, records the attributes of the last card played, and produces the exact same effect.</t>
+  </si>
+  <si>
+    <t>card6N</t>
+  </si>
+  <si>
+    <t>吞噬卡</t>
+  </si>
+  <si>
+    <t>Drain Card</t>
+  </si>
+  <si>
+    <t>card6D</t>
+  </si>
+  <si>
+    <t>玩家吸取指定对象x点生命（对方减少x点生命，玩家回复等量生命）</t>
+  </si>
+  <si>
+    <t>Player drains X life points from a specified target (target loses X life, player recovers equal amount of life).</t>
+  </si>
+  <si>
+    <t>card7N</t>
+  </si>
+  <si>
+    <t>献祭卡</t>
+  </si>
+  <si>
+    <t>Sacrifice Card</t>
+  </si>
+  <si>
+    <t>card7D</t>
+  </si>
+  <si>
+    <t>玩家自身失去x点生命，让指定目标失去2x点生命</t>
+  </si>
+  <si>
+    <t>Player loses X life points, causing a specified target to lose 2X life points.</t>
+  </si>
+  <si>
+    <t>card8N</t>
+  </si>
+  <si>
+    <t>净化卡</t>
+  </si>
+  <si>
+    <t>Purification Card</t>
+  </si>
+  <si>
+    <t>card8D</t>
+  </si>
+  <si>
+    <t>制定对象清除其身上已有的元素异常</t>
+  </si>
+  <si>
+    <t>Clears all elemental abnormalities from a specified target.</t>
+  </si>
+  <si>
+    <t>card9N</t>
+  </si>
+  <si>
+    <t>替身卡</t>
+  </si>
+  <si>
+    <t>Substitute Card</t>
+  </si>
+  <si>
+    <t>card9D</t>
+  </si>
+  <si>
+    <t>将一个替身加入玩家阵营，可以承受伤害或诅咒</t>
+  </si>
+  <si>
+    <t>Adds a decoy to the player's side, which can absorb damage or curses.</t>
+  </si>
+  <si>
+    <t>card10N</t>
+  </si>
+  <si>
+    <t>蛊术卡</t>
+  </si>
+  <si>
+    <t>Curse Card</t>
+  </si>
+  <si>
+    <t>card10D</t>
+  </si>
+  <si>
+    <t>让指定对象获得持续x回合的元素异常</t>
+  </si>
+  <si>
+    <t>Inflicts an elemental abnormality on a specified target lasting for X turns.</t>
+  </si>
+  <si>
+    <t>card11N</t>
+  </si>
+  <si>
+    <t>财宝卡</t>
+  </si>
+  <si>
+    <t>Treasure Card</t>
+  </si>
+  <si>
+    <t>card11D</t>
+  </si>
+  <si>
+    <t>可以直接使用，玩家抽取三张元素卡</t>
+  </si>
+  <si>
+    <t>Can be used directly, player draws three elemental cards.</t>
+  </si>
+  <si>
+    <t>dMap1</t>
+  </si>
+  <si>
+    <t>尖刺部落</t>
+  </si>
+  <si>
+    <t>Spike Tribe</t>
+  </si>
+  <si>
+    <t>dMap2</t>
+  </si>
+  <si>
+    <t>蛇巢</t>
+  </si>
+  <si>
+    <t>Snake Den</t>
+  </si>
+  <si>
+    <t>dMap3</t>
+  </si>
+  <si>
+    <t>幽兰园</t>
+  </si>
+  <si>
+    <t>Orchid Garden</t>
+  </si>
+  <si>
+    <t>dMap4</t>
+  </si>
+  <si>
+    <t>洋脊</t>
+  </si>
+  <si>
+    <t>Ocean Ridge</t>
+  </si>
+  <si>
+    <t>dMap5</t>
+  </si>
+  <si>
+    <t>蚀藻原</t>
+  </si>
+  <si>
+    <t>Corrosive Algae Field</t>
+  </si>
+  <si>
+    <t>dMap6</t>
+  </si>
+  <si>
+    <t>废弃碳矿</t>
+  </si>
+  <si>
+    <t>Derelict Coal Mine</t>
+  </si>
+  <si>
+    <t>dMap7</t>
+  </si>
+  <si>
+    <t>毒瘴林</t>
+  </si>
+  <si>
+    <t>Toxic Mist Woods</t>
+  </si>
+  <si>
+    <t>dMap8</t>
+  </si>
+  <si>
+    <t>破旧古船</t>
+  </si>
+  <si>
+    <t>Worn Old Ship</t>
+  </si>
+  <si>
+    <t>dMap9</t>
+  </si>
+  <si>
+    <t>靛蓝菇群</t>
+  </si>
+  <si>
+    <t>Cobalt Fungi Grove</t>
+  </si>
+  <si>
+    <t>dMap10</t>
+  </si>
+  <si>
+    <t>塔沽冢</t>
+  </si>
+  <si>
+    <t>Tagu Tomb</t>
+  </si>
+  <si>
+    <t>dMap11</t>
+  </si>
+  <si>
+    <t>塔沽核心</t>
+  </si>
+  <si>
+    <t>Tagu Core</t>
+  </si>
+  <si>
+    <t>dMap12</t>
+  </si>
+  <si>
+    <t>鹦鹉螺乡</t>
+  </si>
+  <si>
+    <t>Nautilus Township</t>
+  </si>
+  <si>
+    <t>dMap13</t>
+  </si>
+  <si>
+    <t>乱石窟</t>
+  </si>
+  <si>
+    <t>Jumbled Rock Cave</t>
+  </si>
+  <si>
+    <t>dMap14</t>
+  </si>
+  <si>
+    <t>淤莲池</t>
+  </si>
+  <si>
+    <t>Murky Lotus Pool</t>
+  </si>
+  <si>
+    <t>cMap1</t>
+  </si>
+  <si>
+    <t>cMap2</t>
+  </si>
+  <si>
+    <t>cMap3</t>
+  </si>
+  <si>
+    <t>芳兰园</t>
+  </si>
+  <si>
+    <t>Fragrant Orchid Garden</t>
+  </si>
+  <si>
+    <t>cMap4</t>
+  </si>
+  <si>
+    <t>cMap5</t>
+  </si>
+  <si>
+    <t>熔藻原</t>
+  </si>
+  <si>
+    <t>Magma Algae Field</t>
+  </si>
+  <si>
+    <t>cMap6</t>
+  </si>
+  <si>
+    <t>地底碳矿</t>
+  </si>
+  <si>
+    <t>Underground Coal Mine</t>
+  </si>
+  <si>
+    <t>cMap7</t>
+  </si>
+  <si>
+    <t>薄雾镇</t>
+  </si>
+  <si>
+    <t>Misty Town</t>
+  </si>
+  <si>
+    <t>cMap8</t>
+  </si>
+  <si>
+    <t>船港</t>
+  </si>
+  <si>
+    <t>Boat Port</t>
+  </si>
+  <si>
+    <t>cMap9</t>
+  </si>
+  <si>
+    <t>密林菇群</t>
+  </si>
+  <si>
+    <t>Deepwood Fungi Grove</t>
+  </si>
+  <si>
+    <t>cMap10</t>
+  </si>
+  <si>
+    <t>cMap11</t>
+  </si>
+  <si>
+    <t>cMap12</t>
+  </si>
+  <si>
+    <t>cMap13</t>
+  </si>
+  <si>
+    <t>冰晶石窟</t>
+  </si>
+  <si>
+    <t>Frozen Crystal Cave</t>
+  </si>
+  <si>
+    <t>cMap14</t>
+  </si>
+  <si>
+    <t>莲池</t>
+  </si>
+  <si>
+    <t>Lotus Pool</t>
+  </si>
+  <si>
+    <t>cMap15</t>
+  </si>
+  <si>
+    <t>画廊</t>
+  </si>
+  <si>
+    <t>Gallery</t>
+  </si>
+  <si>
+    <t>canInput</t>
+  </si>
+  <si>
+    <t>材料栏</t>
+  </si>
+  <si>
+    <t>Materials Inventory</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>已投入</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>startForging</t>
+  </si>
+  <si>
+    <t>点击开始锻造</t>
+  </si>
+  <si>
+    <t>Click to start forging</t>
+  </si>
+  <si>
+    <t>ask0</t>
+  </si>
+  <si>
+    <t>这里是做什么的</t>
+  </si>
+  <si>
+    <t>What is this for?</t>
+  </si>
+  <si>
+    <t>ask1</t>
+  </si>
+  <si>
+    <t>购买资源</t>
+  </si>
+  <si>
+    <t>Purchase resources</t>
+  </si>
+  <si>
+    <t>ask2</t>
+  </si>
+  <si>
+    <t>什么是消耗类卡牌和非消耗类卡牌</t>
+  </si>
+  <si>
+    <t>What are consumable cards and non-consumable cards</t>
+  </si>
+  <si>
+    <t>ask3</t>
+  </si>
+  <si>
+    <t>锻造获得的物品跟投入材料有什么关系</t>
+  </si>
+  <si>
+    <t>What is the relationship between the items obtained from forging and the materials used?</t>
+  </si>
+  <si>
+    <t>ask4</t>
+  </si>
+  <si>
+    <t>一次最多可以投入多少材料</t>
+  </si>
+  <si>
+    <t>What is the maximum amount of material that can be added at one time?</t>
+  </si>
+  <si>
+    <t>answer0</t>
+  </si>
+  <si>
+    <t>这里是锻造殿，你可以在这里锻造出各种道具和消耗类卡牌。从右边的材料栏中选择材料并投入，左边的锻造鼎就会随机锻造产物。同时，在这里，我将被赋予创造的能力，你可以向我购买一些我可创造的物品。还有什么其他问题都可以问我。</t>
+  </si>
+  <si>
+    <t>This is the Forging Hall, where you can forge various items and consumable cards. Select materials from the material bar on the right and put them in, and the forging cauldron on the left will produce a random item. At the same time, I will be granted the power to create here, and you can buy some of the items I can create from me. You can also ask me any other questions you may have.</t>
+  </si>
+  <si>
+    <t>answer1</t>
+  </si>
+  <si>
+    <t>好的</t>
+  </si>
+  <si>
+    <t>Ok</t>
+  </si>
+  <si>
+    <t>answer2</t>
+  </si>
+  <si>
+    <t>消耗类卡牌指战斗过程中会被消耗的卡牌，包括目标卡、数值卡和元素卡；非消耗类卡牌是指战斗过程中不会被消耗的卡牌，包括全部的打出卡，即战斗过程中具有攻击、防御、重复等效果的卡牌</t>
+  </si>
+  <si>
+    <t>Consumable cards refer to cards that are used up during battle, including target cards, value cards, and element cards; non-consumable cards refer to cards that are not used up during battle, including all play cards, that is, cards that have attack, defense, or repeat effects during battle.</t>
+  </si>
+  <si>
+    <t>answer3</t>
+  </si>
+  <si>
+    <t>想好了我再告诉你</t>
+  </si>
+  <si>
+    <t>I'll tell you once I've decided.</t>
+  </si>
+  <si>
+    <t>askTips0</t>
+  </si>
+  <si>
+    <t>抱歉，当前区域污染严重，锻造殿无法赋予我锻造及交易的能力</t>
+  </si>
+  <si>
+    <t>Sorry, the current area is heavily polluted, and the Forge Hall cannot grant me forging or trading abilities.</t>
+  </si>
+  <si>
+    <t>askTips1</t>
+  </si>
+  <si>
+    <t>请投入锻造材料</t>
+  </si>
+  <si>
+    <t>Please insert the forging materials.</t>
+  </si>
+  <si>
+    <t>askTips2</t>
+  </si>
+  <si>
+    <t>至少需要投入1枚铜币才能进行锻造</t>
+  </si>
+  <si>
+    <t>At least 1 copper coin is required to forge.</t>
+  </si>
+  <si>
+    <t>askTips4</t>
+  </si>
+  <si>
+    <t>投入的锻造定向材料过多，导致锻造混乱，将无法按照预期概率进行产出，请重新投入锻造材料，注意投入的锻造定向材料不要超过10个</t>
+  </si>
+  <si>
+    <t>Too many targeted forging materials have been used, causing forging chaos. Production will not proceed according to the expected probability. Please re-add the forging materials, and make sure not to use more than 10 targeted forging materials.</t>
+  </si>
+  <si>
+    <t>askTips5</t>
+  </si>
+  <si>
+    <t>购买结束</t>
+  </si>
+  <si>
+    <t>Purchase Complete</t>
+  </si>
+  <si>
+    <t>successForging</t>
+  </si>
+  <si>
+    <t>成功锻造：</t>
+  </si>
+  <si>
+    <t>Successfully Forged:</t>
+  </si>
+  <si>
+    <t>endShop</t>
+  </si>
+  <si>
+    <t>结束购买</t>
+  </si>
+  <si>
+    <t>Complete Purchase</t>
+  </si>
+  <si>
+    <t>exFgTips</t>
+  </si>
+  <si>
+    <t>恭喜获得额外产物：</t>
+  </si>
+  <si>
+    <t>Congratulations on receiving an extra item:</t>
+  </si>
+  <si>
+    <t>itemButton0</t>
+  </si>
+  <si>
+    <t>道具</t>
+  </si>
+  <si>
+    <t>Prop</t>
+  </si>
+  <si>
+    <t>itemButton1</t>
+  </si>
+  <si>
+    <t>护符</t>
+  </si>
+  <si>
+    <t>Talisman</t>
+  </si>
+  <si>
+    <t>itemButton2</t>
+  </si>
+  <si>
+    <t>材料</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>itemButton3</t>
+  </si>
+  <si>
+    <t>物品</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>cardsButton0</t>
+  </si>
+  <si>
+    <t>目标卡</t>
+  </si>
+  <si>
+    <t>Target Cards</t>
+  </si>
+  <si>
+    <t>cardsButton1</t>
+  </si>
+  <si>
+    <t>数值卡</t>
+  </si>
+  <si>
+    <t>Number Cards</t>
+  </si>
+  <si>
+    <t>cardsButton2</t>
+  </si>
+  <si>
+    <t>元素卡</t>
+  </si>
+  <si>
+    <t>Element Cards</t>
   </si>
 </sst>
 </file>
@@ -908,9 +1675,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1223,12 +1993,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="25.0909090909091" customWidth="1"/>
-    <col min="2" max="2" width="36.4545454545455" customWidth="1"/>
-    <col min="3" max="3" width="82.4545454545455" customWidth="1"/>
+    <col min="2" max="2" width="61.2090909090909" customWidth="1"/>
+    <col min="3" max="3" width="112.945454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1283,315 +2053,1283 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
         <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
         <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" ht="28" spans="1:3">
       <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" t="s">
         <v>37</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>116</v>
+      </c>
+      <c r="B42" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>118</v>
+      </c>
+      <c r="B43" t="s">
+        <v>119</v>
+      </c>
+      <c r="C43" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>121</v>
+      </c>
+      <c r="B44" t="s">
+        <v>122</v>
+      </c>
+      <c r="C44" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>124</v>
+      </c>
+      <c r="B45" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" t="s">
+        <v>128</v>
+      </c>
+      <c r="C46" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>133</v>
+      </c>
+      <c r="B48" t="s">
+        <v>134</v>
+      </c>
+      <c r="C48" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>136</v>
+      </c>
+      <c r="B49" t="s">
+        <v>137</v>
+      </c>
+      <c r="C49" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" t="s">
+        <v>140</v>
+      </c>
+      <c r="C50" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>142</v>
+      </c>
+      <c r="B51" t="s">
+        <v>143</v>
+      </c>
+      <c r="C51" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>145</v>
+      </c>
+      <c r="B52" t="s">
+        <v>146</v>
+      </c>
+      <c r="C52" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>148</v>
+      </c>
+      <c r="B53" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>151</v>
+      </c>
+      <c r="B54" t="s">
+        <v>152</v>
+      </c>
+      <c r="C54" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>154</v>
+      </c>
+      <c r="B55" t="s">
+        <v>155</v>
+      </c>
+      <c r="C55" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>157</v>
+      </c>
+      <c r="B56" t="s">
+        <v>158</v>
+      </c>
+      <c r="C56" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>160</v>
+      </c>
+      <c r="B57" t="s">
+        <v>161</v>
+      </c>
+      <c r="C57" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>163</v>
+      </c>
+      <c r="B58" t="s">
+        <v>164</v>
+      </c>
+      <c r="C58" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>166</v>
+      </c>
+      <c r="B59" t="s">
+        <v>167</v>
+      </c>
+      <c r="C59" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>169</v>
+      </c>
+      <c r="B60" t="s">
+        <v>170</v>
+      </c>
+      <c r="C60" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>172</v>
+      </c>
+      <c r="B61" t="s">
+        <v>173</v>
+      </c>
+      <c r="C61" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>175</v>
+      </c>
+      <c r="B62" t="s">
+        <v>176</v>
+      </c>
+      <c r="C62" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>178</v>
+      </c>
+      <c r="B63" t="s">
+        <v>179</v>
+      </c>
+      <c r="C63" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>181</v>
+      </c>
+      <c r="B64" t="s">
+        <v>182</v>
+      </c>
+      <c r="C64" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>184</v>
+      </c>
+      <c r="B65" t="s">
+        <v>185</v>
+      </c>
+      <c r="C65" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>187</v>
+      </c>
+      <c r="B66" t="s">
+        <v>188</v>
+      </c>
+      <c r="C66" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>190</v>
+      </c>
+      <c r="B67" t="s">
+        <v>191</v>
+      </c>
+      <c r="C67" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>193</v>
+      </c>
+      <c r="B68" t="s">
+        <v>194</v>
+      </c>
+      <c r="C68" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>196</v>
+      </c>
+      <c r="B69" t="s">
+        <v>197</v>
+      </c>
+      <c r="C69" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>199</v>
+      </c>
+      <c r="B70" t="s">
+        <v>200</v>
+      </c>
+      <c r="C70" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>202</v>
+      </c>
+      <c r="B71" t="s">
+        <v>203</v>
+      </c>
+      <c r="C71" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>205</v>
+      </c>
+      <c r="B72" t="s">
+        <v>206</v>
+      </c>
+      <c r="C72" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>208</v>
+      </c>
+      <c r="B73" t="s">
+        <v>209</v>
+      </c>
+      <c r="C73" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>211</v>
+      </c>
+      <c r="B74" t="s">
+        <v>212</v>
+      </c>
+      <c r="C74" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>214</v>
+      </c>
+      <c r="B75" t="s">
+        <v>215</v>
+      </c>
+      <c r="C75" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>217</v>
+      </c>
+      <c r="B76" t="s">
+        <v>218</v>
+      </c>
+      <c r="C76" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>220</v>
+      </c>
+      <c r="B77" t="s">
+        <v>221</v>
+      </c>
+      <c r="C77" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>223</v>
+      </c>
+      <c r="B78" t="s">
+        <v>224</v>
+      </c>
+      <c r="C78" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>226</v>
+      </c>
+      <c r="B79" t="s">
+        <v>227</v>
+      </c>
+      <c r="C79" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>229</v>
+      </c>
+      <c r="B80" t="s">
+        <v>188</v>
+      </c>
+      <c r="C80" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>230</v>
+      </c>
+      <c r="B81" t="s">
+        <v>191</v>
+      </c>
+      <c r="C81" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>231</v>
+      </c>
+      <c r="B82" t="s">
+        <v>232</v>
+      </c>
+      <c r="C82" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>234</v>
+      </c>
+      <c r="B83" t="s">
+        <v>197</v>
+      </c>
+      <c r="C83" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>235</v>
+      </c>
+      <c r="B84" t="s">
+        <v>236</v>
+      </c>
+      <c r="C84" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>238</v>
+      </c>
+      <c r="B85" t="s">
+        <v>239</v>
+      </c>
+      <c r="C85" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>241</v>
+      </c>
+      <c r="B86" t="s">
+        <v>242</v>
+      </c>
+      <c r="C86" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>244</v>
+      </c>
+      <c r="B87" t="s">
+        <v>245</v>
+      </c>
+      <c r="C87" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>247</v>
+      </c>
+      <c r="B88" t="s">
+        <v>248</v>
+      </c>
+      <c r="C88" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>250</v>
+      </c>
+      <c r="B89" t="s">
+        <v>215</v>
+      </c>
+      <c r="C89" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>251</v>
+      </c>
+      <c r="B90" t="s">
+        <v>218</v>
+      </c>
+      <c r="C90" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>252</v>
+      </c>
+      <c r="B91" t="s">
+        <v>221</v>
+      </c>
+      <c r="C91" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>253</v>
+      </c>
+      <c r="B92" t="s">
+        <v>254</v>
+      </c>
+      <c r="C92" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>256</v>
+      </c>
+      <c r="B93" t="s">
+        <v>257</v>
+      </c>
+      <c r="C93" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>259</v>
+      </c>
+      <c r="B94" t="s">
+        <v>260</v>
+      </c>
+      <c r="C94" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>262</v>
+      </c>
+      <c r="B95" t="s">
+        <v>263</v>
+      </c>
+      <c r="C95" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>265</v>
+      </c>
+      <c r="B96" t="s">
+        <v>266</v>
+      </c>
+      <c r="C96" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>268</v>
+      </c>
+      <c r="B97" t="s">
+        <v>269</v>
+      </c>
+      <c r="C97" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>271</v>
+      </c>
+      <c r="B98" t="s">
+        <v>272</v>
+      </c>
+      <c r="C98" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>274</v>
+      </c>
+      <c r="B99" t="s">
+        <v>275</v>
+      </c>
+      <c r="C99" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
+        <v>277</v>
+      </c>
+      <c r="B100" t="s">
+        <v>278</v>
+      </c>
+      <c r="C100" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>280</v>
+      </c>
+      <c r="B101" t="s">
+        <v>281</v>
+      </c>
+      <c r="C101" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
+        <v>283</v>
+      </c>
+      <c r="B102" t="s">
+        <v>284</v>
+      </c>
+      <c r="C102" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>286</v>
+      </c>
+      <c r="B103" t="s">
+        <v>287</v>
+      </c>
+      <c r="C103" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
+        <v>289</v>
+      </c>
+      <c r="B104" t="s">
+        <v>290</v>
+      </c>
+      <c r="C104" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
+        <v>292</v>
+      </c>
+      <c r="B105" t="s">
+        <v>293</v>
+      </c>
+      <c r="C105" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
+        <v>295</v>
+      </c>
+      <c r="B106" t="s">
+        <v>296</v>
+      </c>
+      <c r="C106" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
+        <v>298</v>
+      </c>
+      <c r="B107" t="s">
+        <v>299</v>
+      </c>
+      <c r="C107" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
+        <v>301</v>
+      </c>
+      <c r="B108" t="s">
+        <v>302</v>
+      </c>
+      <c r="C108" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
+        <v>304</v>
+      </c>
+      <c r="B109" t="s">
+        <v>305</v>
+      </c>
+      <c r="C109" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
+        <v>307</v>
+      </c>
+      <c r="B110" t="s">
+        <v>308</v>
+      </c>
+      <c r="C110" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>310</v>
+      </c>
+      <c r="B111" t="s">
+        <v>311</v>
+      </c>
+      <c r="C111" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>313</v>
+      </c>
+      <c r="B112" t="s">
+        <v>314</v>
+      </c>
+      <c r="C112" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
+        <v>316</v>
+      </c>
+      <c r="B113" t="s">
+        <v>317</v>
+      </c>
+      <c r="C113" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
+        <v>319</v>
+      </c>
+      <c r="B114" t="s">
+        <v>320</v>
+      </c>
+      <c r="C114" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
+        <v>322</v>
+      </c>
+      <c r="B115" t="s">
+        <v>323</v>
+      </c>
+      <c r="C115" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>325</v>
+      </c>
+      <c r="B116" t="s">
+        <v>326</v>
+      </c>
+      <c r="C116" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
+        <v>328</v>
+      </c>
+      <c r="B117" t="s">
+        <v>329</v>
+      </c>
+      <c r="C117" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
+        <v>331</v>
+      </c>
+      <c r="B118" t="s">
+        <v>332</v>
+      </c>
+      <c r="C118" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
+        <v>334</v>
+      </c>
+      <c r="B119" t="s">
+        <v>335</v>
+      </c>
+      <c r="C119" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
+        <v>337</v>
+      </c>
+      <c r="B120" t="s">
+        <v>338</v>
+      </c>
+      <c r="C120" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
+        <v>340</v>
+      </c>
+      <c r="B121" t="s">
+        <v>341</v>
+      </c>
+      <c r="C121" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
